--- a/public/seller-stock-template.xlsx
+++ b/public/seller-stock-template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accounts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +38,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2937"/>
+        <fgColor rgb="00FFF3D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -423,14 +422,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,66 +438,48 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2FA</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Email Password</t>
+          <t>COOKIES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100012345678901</t>
+          <t>61564510651112</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>examplePass1</t>
+          <t>Shovon@22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JBSWY3DPEHPK3PXP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>mail@example.com</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>mailPass1</t>
+          <t>c_user=61564510651112; xs=38:0lKmJqoYojU7rQ:2:1776870455:-1:-1; fr=0Xc1qdBAVLAB4TiGr.AWeqasxVd-WtWDW8vVj9BFnLP5McgvmaMUhfjcswX3yAZfnSGGw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100098765432109</t>
+          <t>100010709204979</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>examplePass2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>Shovon@24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>wd=706x919; datr=NuToaXxxx; c_user=100010709204979; xs=18:abcdEFG:2:1776870455:-1:-1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
